--- a/data/trans_orig/ProbViv_estruc-Edad-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_estruc-Edad-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9621</t>
+          <t>9603</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>10450</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17878</t>
+          <t>17652</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47890</t>
+          <t>47908</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54579</t>
+          <t>54588</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51013</t>
+          <t>50994</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57881</t>
+          <t>57655</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101077</t>
+          <t>101303</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111311</t>
+          <t>110991</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>10887</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25576</t>
+          <t>25486</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16086</t>
+          <t>16042</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31645</t>
+          <t>30998</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29533</t>
+          <t>29410</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50242</t>
+          <t>51144</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>133723</t>
+          <t>133813</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>148690</t>
+          <t>148412</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>150909</t>
+          <t>151556</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>166468</t>
+          <t>166512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>291611</t>
+          <t>290709</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>312320</t>
+          <t>312443</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,4%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12386</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30839</t>
+          <t>31873</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,82 +1431,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>17792</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>26195</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>8,41%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>12,38%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>37568</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>27434</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>51462</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>7,12%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,74%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17792</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10661</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>27033</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>12,78%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>37568</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>26465</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>51258</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>9,75%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143049</t>
+          <t>142015</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161502</t>
+          <t>161634</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,82 +1544,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>92,95%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>193755</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>185352</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>200146</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>91,59%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>87,62%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>94,61%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>347866</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>333972</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>358000</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>90,25%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>86,65%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>92,88%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>193755</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>184514</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>200886</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>91,59%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>87,22%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>94,96%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>347866</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>334176</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>358969</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>90,25%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>86,7%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15510</t>
+          <t>14824</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32720</t>
+          <t>32420</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18125</t>
+          <t>18285</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37576</t>
+          <t>37663</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37892</t>
+          <t>37733</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64877</t>
+          <t>63858</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>241738</t>
+          <t>242038</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>258948</t>
+          <t>259634</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>267907</t>
+          <t>267820</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>287358</t>
+          <t>287198</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>515064</t>
+          <t>516083</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>542049</t>
+          <t>542208</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51383</t>
+          <t>50689</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83388</t>
+          <t>81698</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59503</t>
+          <t>58030</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88982</t>
+          <t>90503</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117506</t>
+          <t>117272</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160601</t>
+          <t>159766</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>581768</t>
+          <t>583458</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>613773</t>
+          <t>614467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>672046</t>
+          <t>670525</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>701525</t>
+          <t>702998</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1265583</t>
+          <t>1266418</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1308678</t>
+          <t>1308912</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ProbViv_estruc-Edad-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_estruc-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5725</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3286</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9322</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,33%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18,45%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5671</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2923</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9603</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,86%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6344</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10450</t>
+          <t>9236</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12015</t>
+          <t>10986</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>7537</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17652</t>
+          <t>16568</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>44812</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>41215</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>47251</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,67%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>81,55%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,5%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>51840</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>47908</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54588</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>90,14%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>83,3%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,92%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55100</t>
+          <t>46829</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50994</t>
+          <t>42854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57655</t>
+          <t>49558</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>106940</t>
+          <t>91641</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101303</t>
+          <t>86059</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110991</t>
+          <t>95090</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19178</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13429</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27075</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,17%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,52%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,19%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>16445</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10887</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>25486</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>10,32%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,83%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22669</t>
+          <t>13530</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16042</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30998</t>
+          <t>19844</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>39114</t>
+          <t>32708</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29410</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51144</t>
+          <t>41663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>138344</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>130447</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>144093</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,83%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,81%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>91,48%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>142854</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>133813</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>148412</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>89,68%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>159885</t>
+          <t>131988</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>151556</t>
+          <t>125674</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>166512</t>
+          <t>136272</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>302739</t>
+          <t>270331</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>290709</t>
+          <t>261376</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>312443</t>
+          <t>277639</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,107 +1406,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17505</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11305</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>27010</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,79%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,68%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,56%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>19776</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12254</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>31873</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>17972</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12167</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>25545</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>10,24%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>35477</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>26412</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>47732</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>9,47%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>7,05%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,33%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17792</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11401</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>26195</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>12,38%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>37568</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>27434</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>51462</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>9,75%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>7,12%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -1519,107 +1519,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>181664</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>172159</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>187864</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,21%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,44%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,32%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>154112</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>142015</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>161634</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>88,63%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>81,67%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>157546</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>149973</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>163351</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>89,76%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>85,45%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>93,07%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>339209</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>326954</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>348274</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>90,53%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>87,26%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>92,95%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>193755</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>185352</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>200146</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>91,59%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>87,62%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>94,61%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>347866</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>333972</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>358000</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>90,25%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>86,65%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22914</t>
+          <t>25776</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14824</t>
+          <t>18211</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32420</t>
+          <t>36219</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26524</t>
+          <t>24593</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18285</t>
+          <t>17308</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37663</t>
+          <t>34146</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>49438</t>
+          <t>50368</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37733</t>
+          <t>39444</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63858</t>
+          <t>64990</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>266869</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>256426</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>274434</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,19%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,62%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,78%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>307</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>251544</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>242038</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>259634</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>91,65%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,19%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,6%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>278959</t>
+          <t>230885</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>267820</t>
+          <t>221332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>287198</t>
+          <t>238170</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>530503</t>
+          <t>497754</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>516083</t>
+          <t>483132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>542208</t>
+          <t>508678</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>68184</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>54905</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>83074</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,74%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>64805</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>50689</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>81698</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,74%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>73329</t>
+          <t>61356</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58030</t>
+          <t>49795</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90503</t>
+          <t>75604</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>138135</t>
+          <t>129540</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117272</t>
+          <t>112229</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159766</t>
+          <t>148939</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>631688</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>616798</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>644967</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>88,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,16%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>848</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>600351</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>583458</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>614467</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>90,26%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,72%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>877</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>687699</t>
+          <t>567247</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>670525</t>
+          <t>552999</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>702998</t>
+          <t>578808</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1288049</t>
+          <t>1198935</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1266418</t>
+          <t>1179536</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1308912</t>
+          <t>1216246</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426184</t>
+          <t>1328475</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426184</t>
+          <t>1328475</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426184</t>
+          <t>1328475</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
